--- a/loan_application_forms/045_gift_letter_for_mortgage--loan_application_forms.xlsx
+++ b/loan_application_forms/045_gift_letter_for_mortgage--loan_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>primary_residence</t>
+          <t>primary_vacation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Primary Residence</t>
+          <t>Primary Vacation</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>primary_vacation</t>
+          <t>primary_investment_property</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Primary Vacation</t>
+          <t>Primary Investment Property</t>
         </is>
       </c>
     </row>
@@ -1216,29 +1216,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>primary_investment_property</t>
+          <t>primary_other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Primary Investment Property</t>
+          <t>Primary Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>donor_relationship_choices</t>
+          <t>gift_purpose_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>primary_other</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Primary Other</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>primary_residence</t>
+          <t>vacation_home</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Primary Residence</t>
+          <t>Vacation Home</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>vacation_home</t>
+          <t>investment_property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Vacation Home</t>
+          <t>Investment Property</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Investment Property</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>gift_purpose_choices</t>
+          <t>property_type_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>primary_residence</t>
+          <t>vacation_home</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primary Residence</t>
+          <t>Vacation Home</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>vacation_home</t>
+          <t>investment_property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vacation Home</t>
+          <t>Investment Property</t>
         </is>
       </c>
     </row>
@@ -1352,29 +1352,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Investment Property</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>property_type_choices</t>
+          <t>loan_term_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>30_years</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>30 Years</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30_years</t>
+          <t>15_years</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>30 Years</t>
+          <t>15 Years</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15_years</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15 Years</t>
+          <t>5 Years</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>loan_term_choices</t>
+          <t>loan_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5_years</t>
+          <t>fixed_rate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5 Years</t>
+          <t>Fixed Rate</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fixed_rate</t>
+          <t>variable_rate</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Fixed Rate</t>
+          <t>Variable Rate</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>variable_rate</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Variable Rate</t>
+          <t>Hybrid</t>
         </is>
       </c>
     </row>
@@ -1471,29 +1471,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>interest_only</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Interest Only</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>loan_type_choices</t>
+          <t>collateral_type_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>interest_only</t>
+          <t>primary_residence</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Interest Only</t>
+          <t>Primary Residence</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>primary_residence</t>
+          <t>vacation_home</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Primary Residence</t>
+          <t>Vacation Home</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vacation_home</t>
+          <t>investment_property</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Vacation Home</t>
+          <t>Investment Property</t>
         </is>
       </c>
     </row>
@@ -1539,29 +1539,29 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>investment_property</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Investment Property</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>collateral_type_choices</t>
+          <t>loan_status_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1573,27 +1573,10 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>paid_off</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>loan_status_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>paid_off</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
         <is>
           <t>Paid Off</t>
         </is>
